--- a/currentbuild/StructureDefinition-auditevent-patient.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T05:44:14+00:00</t>
+    <t>2024-06-04T06:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-auditevent-patient.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T06:11:20+00:00</t>
+    <t>2024-06-06T18:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
